--- a/GATEWAY/A1#111NUVIA1/NUVIA/VAIDOC/4.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111NUVIA1/NUVIA/VAIDOC/4.0/report-checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nuvia/Projects/fse/invio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nuvia/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349C1546-EDF3-8644-9DC6-2B6406D10EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB4D2F5-478C-1347-80D0-C2011F569983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="40180" windowHeight="22540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38400" yWindow="-1440" windowWidth="40960" windowHeight="23040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="273">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -962,9 +962,6 @@
     <t>subject_application_id: VAIDOC</t>
   </si>
   <si>
-    <t>Non obbligatorio in ottemperanza a quanto espresso dal Decreto settembre 2023</t>
-  </si>
-  <si>
     <t>Non obbligatorio in ottemperanza a quanto espresso dal Decreto 7 settembre 2023</t>
   </si>
   <si>
@@ -1004,6 +1001,135 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.120.4.4.8fe46b71d98546dc779f4a7f4859b056b254bbe56b59baa550333b2c46441c87.c58e9318d2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>Il test richiede un JWT volutamente non conforme, ottenuto non valorizzando il claim purpose_of_use. Nell’applicativo il token viene generato automaticamente e i claim applicativi sono valorizzati secondo regole predefinite coerenti con l’operazione eseguita, senza possibilità di impostare manualmente valori arbitrari non ammessi. Non è pertanto possibile generare un JWT con action_id non conforme ai fini del test negativo.</t>
+  </si>
+  <si>
+    <t>Il test richiede un JWT volutamente non conforme, ottenuto valorizzando il claim action_id con un valore non ammesso (TEST). Nell’applicativo il token viene generato automaticamente e i claim applicativi sono valorizzati secondo regole predefinite coerenti con l’operazione eseguita, senza possibilità di impostare manualmente valori arbitrari non ammessi. Non è pertanto possibile generare un JWT con action_id non conforme ai fini del test negativo.</t>
+  </si>
+  <si>
+    <t>Gestione applicativa dell'errore semantico sul codice fiscale: Il codice fiscale viene normalizzato automaticamente in maiuscolo prima del salvataggio; non è quindi possibile generare il CDA2 con codice fiscale in minuscolo richiesto dal test.</t>
+  </si>
+  <si>
+    <t>I dati anagrafici gestiti dall’applicativo, inclusi gli indirizzi di residenza, sono soggetti a controlli preventivi che richiedono la valorizzazione degli elementi minimi obbligatori (es. nazione, comune e indirizzo). Non è pertanto possibile salvare o utilizzare dati anagrafici incompleti e, di conseguenza, generare un CDA2 contenente un elemento addr privo dei sotto-elementi richiesti (country, city, streetAddressLine), come previsto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I dati anagrafici del paziente gestiti dall’applicativo sono soggetti a controlli preventivi che richiedono la valorizzazione degli elementi minimi obbligatori del nome, in particolare given (nome) e family (cognome). Non è pertanto possibile salvare o utilizzare anagrafiche incomplete e, di conseguenza, generare un CDA2 contenente un elemento name privo dei sotto-elementi richiesti, come previsto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I campi codificati gestiti dall’applicativo sono soggetti a vincoli sui valori ammessi, derivanti da domini predefiniti e/o tabelle di codifica controllate. Non è pertanto possibile valorizzare tali elementi con codici non previsti o non censiti nei sistemi di codifica di riferimento. Di conseguenza, non è possibile generare un CDA2 contenente valori terminologicamente non conformi, come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il CDA2 viene generato programmaticamente dall’applicativo sulla base di template strutturali conformi agli schemi XML (XSD) di riferimento. La costruzione del documento non prevede la possibilità di omettere elementi obbligatori della struttura (es. realmCode, typeId, templateId, id all’interno del nodo order). Non è pertanto possibile generare un CDA2 sintatticamente non conforme come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I codici associati alle sezioni del referto sono determinati programmaticamente dall’applicativo sulla base della tipologia di documento e sono mappati su valori LOINC predefiniti e controllati. Non è pertanto possibile valorizzare l’elemento section/code con codici non ammessi o non coerenti con il dominio previsto, e quindi generare il CDA2 semanticamente non conforme richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Le informazioni relative al campione biologico (specimen) sono gestite in modo strutturato dall’applicativo e la relativa codifica è determinata programmaticamente sulla base dei dati inseriti. La generazione del CDA2 prevede la valorizzazione automatica degli elementi obbligatori della struttura, incluso l’elemento code del nodo specimenPlayingEntity. Non è pertanto possibile generare un CDA2 in cui tale elemento risulti assente, come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Le strutture di tipo organizer (es. pannelli di esami con classCode='BATTERY') sono generate programmaticamente dall’applicativo sulla base della configurazione delle prestazioni e includono automaticamente gli elementi obbligatori previsti dal modello CDA2, tra cui l’elemento organizer/code. Non è pertanto possibile generare un CDA2 contenente un organizer di tipo BATTERY privo del relativo code, come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I codici fiscali gestiti dall’applicativo sono soggetti a normalizzazione preventiva prima del salvataggio, con conversione automatica in caratteri maiuscoli. Non è pertanto possibile generare un CDA2 contenente un codice fiscale formalmente valorizzato ma semanticamente non conforme per uso di caratteri minuscoli, come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I dati anagrafici gestiti dall’applicativo, inclusi gli indirizzi di residenza, sono soggetti a controlli preventivi che richiedono la valorizzazione degli elementi minimi obbligatori (es. comune di residenza). Non è pertanto possibile salvare o utilizzare indirizzi incompleti e, di conseguenza, generare un CDA2 contenente un elemento addr privo delle informazioni richieste, come previsto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I dati anagrafici del paziente gestiti dall’applicativo sono soggetti a controlli preventivi che richiedono la valorizzazione degli elementi minimi obbligatori, in particolare nome (given) e cognome (family). Non è pertanto possibile salvare o utilizzare anagrafiche incomplete e, di conseguenza, generare un CDA2 contenente un elemento name privo dei sotto-elementi richiesti, come previsto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il sesso del paziente è gestito dall’applicativo mediante un dominio di valori predefiniti e controllati (Maschio, Femmina, N/A). Tale informazione viene mappata automaticamente nel CDA2 secondo le codifiche previste, senza possibilità di inserimento di valori arbitrari o non ammessi. Non è pertanto possibile generare un CDA2 contenente valori terminologicamente non conformi, come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il nodo ClinicalDocument/participant è opzionale secondo il modello CDA2 e non è gestito in modo strutturato dall’applicativo. Non essendo prevista la sua valorizzazione, non è possibile popolare il relativo elemento code, né introdurre valori terminologicamente non conformi come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>In presenza del nodo inFulfillmentOf, l’elemento order/id viene sempre valorizzato programmaticamente; non è pertanto possibile generare il caso sintatticamente errato richiesto dal test.</t>
+  </si>
+  <si>
+    <t>Il CDA2 di radiologia viene generato programmaticamente dall’applicativo sulla base di template strutturali conformi agli schemi XML (XSD) di riferimento. La costruzione del documento prevede la valorizzazione automatica degli elementi obbligatori e non consente la generazione di nodi incompleti o strutturalmente non validi. Non è pertanto possibile produrre un CDA2 sintatticamente non conforme come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>L’applicativo genera la sezione “Referto” in modo programmatico e ne garantisce la valorizzazione coerente con i dati disponibili; in assenza del contenuto minimo richiesto il documento non viene prodotto. Non è quindi possibile generare, tramite il normale comportamento applicativo, il CDA2 semanticamente errato richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>La sezione “Precedenti esami eseguiti” è opzionale secondo il modello CDA2 di radiologia e non è gestita in modo strutturato dall’applicativo. In assenza di gestione applicativa della sezione, la stessa non viene valorizzata nel documento CDA2; non è pertanto possibile generare condizioni di errore semantico su tale sezione come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>La sezione “DICOM Object Catalog” è opzionale secondo il modello CDA2 di radiologia e non è gestita in modo strutturato dall’applicativo. In assenza di gestione applicativa, la sezione non viene inclusa nel documento CDA2; non è pertanto possibile generare condizioni di errore semantico su tale sezione come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>La sezione “Storia clinica” è opzionale secondo il modello CDA2 di radiologia e non è gestita in modo strutturato dall’applicativo. In assenza di gestione applicativa, la sezione non viene inclusa nel documento CDA2; non è pertanto possibile generare condizioni di errore semantico su tale sezione come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>La sezione “Quesito Diagnostico” è opzionale secondo il modello CDA2 di radiologia e non è gestita in modo strutturato dall’applicativo. In assenza di gestione applicativa, la sezione non viene inclusa nel documento CDA2 e non vengono valorizzati i relativi elementi codificati (entry/code); non è pertanto possibile generare errori terminologici su tale sezione come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il nodo ClinicalDocument/documentationOf è opzionale secondo il modello CDA2 di radiologia e non è gestito in modo strutturato dall’applicativo. In assenza di gestione applicativa, il nodo non viene valorizzato né incluso nel documento CDA2; non è pertanto possibile generare condizioni di errore semantico su tale elemento come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I codici fiscali sono soggetti a controlli applicativi e a normalizzazione automatica in fase di inserimento e salvataggio, che ne garantisce la conformità al formato previsto (uppercase e lunghezza/struttura valida). Il dato viene quindi riportato nel CDA2 in forma normalizzata, senza possibilità di inserimento di caratteri non conformi (es. minuscoli). Non è pertanto possibile generare un CDA2 contenente un codice fiscale semanticamente non valido come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I dati di indirizzo del paziente sono soggetti a controlli applicativi che ne garantiscono la completezza minima obbligatoria in fase di inserimento e salvataggio. In particolare, non è consentito registrare indirizzi privi delle informazioni essenziali (es. comune di residenza). Il dato viene quindi riportato nel CDA2 sempre in forma completa; non è pertanto possibile generare un documento con informazioni mancanti come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>I dati anagrafici del paziente sono soggetti a controlli applicativi che ne garantiscono la completezza in fase di inserimento e generazione del referto. In particolare, la valorizzazione degli elementi obbligatori (es. nome e cognome) è vincolante ai fini della produzione del documento. Il CDA2 viene pertanto generato esclusivamente in presenza di anagrafica completa; non è possibile produrre documenti con dati mancanti come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il sesso del paziente è gestito dall’applicativo mediante un dominio di valori predefiniti e controllati (Maschio, Femmina, N/A). Tale informazione è soggetta a validazione in fase di inserimento e viene mappata automaticamente nel CDA2 secondo le codifiche previste, senza possibilità di inserimento di valori arbitrari o non ammessi. Non è pertanto possibile generare un CDA2 contenente valori terminologicamente non conformi come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Le prestazioni sono gestite dall’applicativo con obbligo di valorizzazione del relativo codice in fase di inserimento e salvataggio; non è consentita la registrazione di prestazioni prive di codice. Il CDA2 viene generato programmaticamente a partire da tali dati strutturati, garantendo la presenza degli elementi obbligatori previsti dallo schema XML. Non è pertanto possibile produrre un documento con elementi mancanti o strutturalmente non conformi come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>La sezione “Quesito diagnostico” è opzionale secondo il modello CDA2 di specialistica ambulatoriale ed è gestita dall’applicativo solo in presenza di contenuto testuale. In assenza di tale contenuto, la sezione non viene inclusa nel documento CDA2. Non è pertanto possibile generare condizioni di errore semantico su tale sezione, in quanto non valorizzata, come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Le prestazioni sono gestite in modo strutturato dall’applicativo e ciascuna prestazione effettuata genera un corrispondente elemento entry/act nel CDA2. La cardinalità della sezione è quindi garantita automaticamente (almeno un elemento per prestazione), senza possibilità di omissione o inconsistenza rispetto al contenuto del referto. Non è pertanto possibile generare condizioni di errore semantico su tale sezione come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>La sezione prevista dal caso di test è opzionale secondo il modello CDA2 di specialistica ambulatoriale e non è gestita in modo strutturato dall’applicativo. In assenza di gestione applicativa, tale sezione non viene inclusa nel documento CDA2; non è pertanto possibile generare condizioni di errore semantico su tale elemento come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>La sezione “Quesito Diagnostico” è gestita dall’applicativo esclusivamente nella sua componente testuale (text) e non prevede la valorizzazione strutturata dei nodi entry e dei relativi elementi codificati (code). In assenza di gestione di dati codificati, non è possibile generare valori terminologicamente non conformi; non è pertanto possibile produrre l’errore richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il documento CDA2 è sempre sottoposto a firma digitale prima dell’invio, pertanto l’elemento signatureCode viene valorizzato automaticamente con valore conforme (“S”). La valorizzazione del campo è vincolata al processo di firma e non è modificabile manualmente. Non è pertanto possibile generare condizioni di errore semantico su tale elemento come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Non applicabile alla piattaforma Vaidoc in quanto il caso di test riguarda documenti CDA2 di ambito trasfusionale/HLA, che costituiscono una sottotipologia documentale specialistica distinta rispetto al perimetro funzionale oggetto di validazione. Vaidoc non produce né valida tali specifici documenti secondo i template ministeriali trasfusionali; il caso deve quindi considerarsi fuori ambito.</t>
+  </si>
+  <si>
+    <t>Il caso di test richiede la composizione completa di un CDA2 Referto Specialistica Ambulatoriale conforme al template ministeriale del CT25, comprensivo delle section/entry previste nello scenario di riferimento. L’applicativo non gestisce in modo strutturato la specifica sezione/entry richiesta dal caso di test e pertanto non è in grado di produrre il CDA2 conforme necessario per l’esecuzione del test positivo. Il caso risulta quindi non applicabile rispetto al perimetro funzionale implementato.</t>
+  </si>
+  <si>
+    <t>Il caso di test richiede la valorizzazione di uno specifico elemento codificato del CDA2 RSA con un valore terminologicamente non conforme. Tale elemento non è gestito in modo strutturato dall’applicativo, che non ne prevede la compilazione codificata secondo la casistica ministeriale. Non è pertanto possibile riprodurre il caso negativo richiesto dal test.</t>
+  </si>
+  <si>
+    <t>Il CDA2 viene generato programmaticamente dal sistema e la struttura XML risultante è determinata da regole applicative che impediscono la produzione di nodi/attributi sintatticamente incompleti o malformati nella casistica prevista dal test. Non è pertanto possibile generare, tramite il normale flusso applicativo, il documento sintatticamente errato richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il valore dell’attributo code dell’elemento confidentialityCode è gestito dall’applicativo mediante valorizzazione automatica conforme ai vincoli previsti dallo schema CDA2 (tipo cs e pattern non vuoto). Non è consentita la generazione di attributi privi di valore o non conformi al formato richiesto. Il documento CDA2 è inoltre generato programmaticamente sulla base di template strutturali validi, garantendo il rispetto dei vincoli sintattici XML/XSD. Non è pertanto possibile produrre un documento con errori sintattici come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il CDA2 RSA viene generato programmaticamente dall’applicativo; la struttura XML è prodotta secondo regole che impediscono la valorizzazione incompleta o formalmente non valida dell’elemento oggetto del test. Non è quindi possibile generare il documento sintatticamente non conforme richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il caso di test richiede la composizione completa di un CDA2 Referto di Radiologia conforme al template ministeriale del CT26, inclusi gli elementi strutturati previsti nello scenario. L’applicativo non gestisce in modo strutturato la specifica sezione/entry richiesta dal caso di test e pertanto non è in grado di produrre il CDA2 conforme necessario per l’esecuzione del test positivo. Il caso risulta quindi non applicabile rispetto al perimetro implementato.</t>
+  </si>
+  <si>
+    <t>I valori codificati presenti nel CDA2 sono gestiti tramite domini controllati e vincolati a code system standard (es. HL7, LOINC), con mapping applicativo che limita la selezione ai soli codici ammessi. Non è possibile inserire o trasmettere codici arbitrari o non censiti (come "RX" per il code system indicato), in quanto l’applicativo effettua controlli preventivi e utilizza valori predefiniti conformi. Non è pertanto possibile generare un CDA2 contenente errori terminologici come richiesto dal caso di test.</t>
+  </si>
+  <si>
+    <t>Il caso di test richiede la valorizzazione di un elemento codificato del CDA2 RAD con un valore terminologicamente non conforme. L’applicativo applica vincoli sui valori ammessi oppure non gestisce in modo strutturato il nodo codificato previsto dal caso di test; non è pertanto possibile generare il CDA2 con l’errore terminologico richiesto.</t>
+  </si>
+  <si>
+    <t>Il caso di test richiede la valorizzazione di un elemento codificato del CDA2 RSA con un valore terminologicamente non conforme. L’applicativo non consente la generazione di valori codificati arbitrari o non ammessi per l’elemento oggetto del test, oppure non lo gestisce in modo strutturato. Non è pertanto possibile produrre il CDA2 con l’errore terminologico richiesto.</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1139,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1142,8 +1268,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1168,8 +1307,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1500,12 +1645,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1674,6 +1834,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3122,7 +3303,9 @@
     <col min="5" max="5" width="104.83203125" customWidth="1"/>
     <col min="6" max="9" width="33.1640625" customWidth="1"/>
     <col min="10" max="10" width="27.1640625" customWidth="1"/>
-    <col min="11" max="18" width="36.5" customWidth="1"/>
+    <col min="11" max="11" width="36.5" customWidth="1"/>
+    <col min="12" max="12" width="36.5" style="73" customWidth="1"/>
+    <col min="13" max="18" width="36.5" customWidth="1"/>
     <col min="19" max="19" width="27.1640625" customWidth="1"/>
     <col min="20" max="20" width="33.1640625" customWidth="1"/>
     <col min="21" max="21" width="36.5" customWidth="1"/>
@@ -3424,7 +3607,7 @@
         <v>128</v>
       </c>
       <c r="L10" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M10" s="38"/>
       <c r="N10" s="38"/>
@@ -3464,10 +3647,10 @@
         <v>119</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L11" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L11" s="71" t="s">
+        <v>230</v>
       </c>
       <c r="M11" s="38"/>
       <c r="N11" s="38"/>
@@ -3507,10 +3690,10 @@
         <v>119</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L12" s="38" t="s">
-        <v>217</v>
+        <v>127</v>
+      </c>
+      <c r="L12" s="71" t="s">
+        <v>230</v>
       </c>
       <c r="M12" s="38"/>
       <c r="N12" s="38"/>
@@ -3550,10 +3733,10 @@
         <v>119</v>
       </c>
       <c r="K13" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L13" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L13" s="71" t="s">
+        <v>230</v>
       </c>
       <c r="M13" s="38"/>
       <c r="N13" s="38"/>
@@ -3593,10 +3776,10 @@
         <v>119</v>
       </c>
       <c r="K14" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L14" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L14" s="71" t="s">
+        <v>231</v>
       </c>
       <c r="M14" s="38"/>
       <c r="N14" s="38"/>
@@ -3636,10 +3819,10 @@
         <v>119</v>
       </c>
       <c r="K15" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L15" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L15" s="71" t="s">
+        <v>231</v>
       </c>
       <c r="M15" s="38"/>
       <c r="N15" s="38"/>
@@ -3679,10 +3862,10 @@
         <v>119</v>
       </c>
       <c r="K16" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L16" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L16" s="71" t="s">
+        <v>231</v>
       </c>
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
@@ -3730,7 +3913,7 @@
         <v>54</v>
       </c>
       <c r="O17" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P17" s="38" t="s">
         <v>54</v>
@@ -3742,7 +3925,7 @@
         <v>54</v>
       </c>
       <c r="S17" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T17" s="38"/>
       <c r="U17" s="39" t="s">
@@ -3785,7 +3968,7 @@
         <v>54</v>
       </c>
       <c r="O18" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P18" s="38" t="s">
         <v>54</v>
@@ -3797,7 +3980,7 @@
         <v>54</v>
       </c>
       <c r="S18" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T18" s="38"/>
       <c r="U18" s="39" t="s">
@@ -3840,7 +4023,7 @@
         <v>54</v>
       </c>
       <c r="O19" s="38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P19" s="38" t="s">
         <v>54</v>
@@ -3852,7 +4035,7 @@
         <v>54</v>
       </c>
       <c r="S19" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T19" s="38"/>
       <c r="U19" s="39" t="s">
@@ -3887,10 +4070,10 @@
         <v>119</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L20" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L20" s="69" t="s">
+        <v>232</v>
       </c>
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
@@ -3930,10 +4113,10 @@
         <v>119</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L21" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L21" s="71" t="s">
+        <v>233</v>
       </c>
       <c r="M21" s="38"/>
       <c r="N21" s="38"/>
@@ -3973,10 +4156,10 @@
         <v>119</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L22" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L22" s="70" t="s">
+        <v>234</v>
       </c>
       <c r="M22" s="38"/>
       <c r="N22" s="38"/>
@@ -4016,10 +4199,10 @@
         <v>119</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L23" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L23" s="71" t="s">
+        <v>235</v>
       </c>
       <c r="M23" s="38"/>
       <c r="N23" s="38"/>
@@ -4059,10 +4242,10 @@
         <v>119</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L24" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L24" s="71" t="s">
+        <v>236</v>
       </c>
       <c r="M24" s="38"/>
       <c r="N24" s="38"/>
@@ -4102,10 +4285,10 @@
         <v>119</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L25" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L25" s="67" t="s">
+        <v>237</v>
       </c>
       <c r="M25" s="38"/>
       <c r="N25" s="38"/>
@@ -4145,10 +4328,10 @@
         <v>119</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L26" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L26" s="70" t="s">
+        <v>238</v>
       </c>
       <c r="M26" s="38"/>
       <c r="N26" s="38"/>
@@ -4188,10 +4371,10 @@
         <v>119</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L27" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L27" s="67" t="s">
+        <v>239</v>
       </c>
       <c r="M27" s="38"/>
       <c r="N27" s="38"/>
@@ -4231,10 +4414,10 @@
         <v>119</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L28" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L28" s="67" t="s">
+        <v>240</v>
       </c>
       <c r="M28" s="38"/>
       <c r="N28" s="38"/>
@@ -4274,10 +4457,10 @@
         <v>119</v>
       </c>
       <c r="K29" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L29" s="38" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="M29" s="38"/>
       <c r="N29" s="38"/>
@@ -4317,10 +4500,10 @@
         <v>119</v>
       </c>
       <c r="K30" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L30" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L30" s="67" t="s">
+        <v>242</v>
       </c>
       <c r="M30" s="38"/>
       <c r="N30" s="38"/>
@@ -4360,10 +4543,10 @@
         <v>119</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L31" s="38" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="M31" s="38"/>
       <c r="N31" s="38"/>
@@ -4403,10 +4586,10 @@
         <v>119</v>
       </c>
       <c r="K32" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L32" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L32" s="67" t="s">
+        <v>244</v>
       </c>
       <c r="M32" s="38"/>
       <c r="N32" s="38"/>
@@ -4446,10 +4629,10 @@
         <v>119</v>
       </c>
       <c r="K33" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L33" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L33" s="68" t="s">
+        <v>245</v>
       </c>
       <c r="M33" s="38"/>
       <c r="N33" s="38"/>
@@ -4489,10 +4672,10 @@
         <v>119</v>
       </c>
       <c r="K34" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L34" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L34" s="70" t="s">
+        <v>246</v>
       </c>
       <c r="M34" s="38"/>
       <c r="N34" s="38"/>
@@ -4532,10 +4715,10 @@
         <v>119</v>
       </c>
       <c r="K35" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L35" s="38" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="M35" s="38"/>
       <c r="N35" s="38"/>
@@ -4575,10 +4758,10 @@
         <v>119</v>
       </c>
       <c r="K36" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L36" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L36" s="67" t="s">
+        <v>248</v>
       </c>
       <c r="M36" s="38"/>
       <c r="N36" s="38"/>
@@ -4618,10 +4801,10 @@
         <v>119</v>
       </c>
       <c r="K37" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L37" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L37" s="67" t="s">
+        <v>249</v>
       </c>
       <c r="M37" s="38"/>
       <c r="N37" s="38"/>
@@ -4661,10 +4844,10 @@
         <v>119</v>
       </c>
       <c r="K38" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L38" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L38" s="54" t="s">
+        <v>250</v>
       </c>
       <c r="M38" s="38"/>
       <c r="N38" s="38"/>
@@ -4704,10 +4887,10 @@
         <v>119</v>
       </c>
       <c r="K39" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L39" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L39" s="54" t="s">
+        <v>250</v>
       </c>
       <c r="M39" s="38"/>
       <c r="N39" s="38"/>
@@ -4747,10 +4930,10 @@
         <v>119</v>
       </c>
       <c r="K40" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L40" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L40" s="54" t="s">
+        <v>250</v>
       </c>
       <c r="M40" s="38"/>
       <c r="N40" s="38"/>
@@ -4790,10 +4973,10 @@
         <v>119</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L41" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L41" s="54" t="s">
+        <v>250</v>
       </c>
       <c r="M41" s="38"/>
       <c r="N41" s="38"/>
@@ -4833,10 +5016,10 @@
         <v>119</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L42" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L42" s="54" t="s">
+        <v>251</v>
       </c>
       <c r="M42" s="38"/>
       <c r="N42" s="38"/>
@@ -4876,10 +5059,10 @@
         <v>119</v>
       </c>
       <c r="K43" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L43" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L43" s="54" t="s">
+        <v>252</v>
       </c>
       <c r="M43" s="38"/>
       <c r="N43" s="38"/>
@@ -4919,10 +5102,10 @@
         <v>119</v>
       </c>
       <c r="K44" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L44" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L44" s="67" t="s">
+        <v>253</v>
       </c>
       <c r="M44" s="38"/>
       <c r="N44" s="38"/>
@@ -4962,10 +5145,10 @@
         <v>119</v>
       </c>
       <c r="K45" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L45" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L45" s="67" t="s">
+        <v>254</v>
       </c>
       <c r="M45" s="38"/>
       <c r="N45" s="38"/>
@@ -5005,10 +5188,10 @@
         <v>119</v>
       </c>
       <c r="K46" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L46" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L46" s="67" t="s">
+        <v>255</v>
       </c>
       <c r="M46" s="38"/>
       <c r="N46" s="38"/>
@@ -5048,10 +5231,10 @@
         <v>119</v>
       </c>
       <c r="K47" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L47" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L47" s="54" t="s">
+        <v>256</v>
       </c>
       <c r="M47" s="38"/>
       <c r="N47" s="38"/>
@@ -5091,10 +5274,10 @@
         <v>119</v>
       </c>
       <c r="K48" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L48" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L48" s="54" t="s">
+        <v>245</v>
       </c>
       <c r="M48" s="38"/>
       <c r="N48" s="38"/>
@@ -5134,10 +5317,10 @@
         <v>119</v>
       </c>
       <c r="K49" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L49" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L49" s="54" t="s">
+        <v>257</v>
       </c>
       <c r="M49" s="38"/>
       <c r="N49" s="38"/>
@@ -5177,10 +5360,10 @@
         <v>119</v>
       </c>
       <c r="K50" s="38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L50" s="38" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="M50" s="38"/>
       <c r="N50" s="38"/>
@@ -5220,10 +5403,10 @@
         <v>119</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L51" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L51" s="54" t="s">
+        <v>258</v>
       </c>
       <c r="M51" s="38"/>
       <c r="N51" s="38"/>
@@ -5263,10 +5446,10 @@
         <v>119</v>
       </c>
       <c r="K52" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L52" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L52" s="54" t="s">
+        <v>259</v>
       </c>
       <c r="M52" s="38"/>
       <c r="N52" s="38"/>
@@ -5306,10 +5489,10 @@
         <v>119</v>
       </c>
       <c r="K53" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L53" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L53" s="54" t="s">
+        <v>260</v>
       </c>
       <c r="M53" s="38"/>
       <c r="N53" s="38"/>
@@ -5349,10 +5532,10 @@
         <v>119</v>
       </c>
       <c r="K54" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L54" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L54" s="54" t="s">
+        <v>260</v>
       </c>
       <c r="M54" s="38"/>
       <c r="N54" s="38"/>
@@ -5392,10 +5575,10 @@
         <v>119</v>
       </c>
       <c r="K55" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L55" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L55" s="54" t="s">
+        <v>260</v>
       </c>
       <c r="M55" s="38"/>
       <c r="N55" s="38"/>
@@ -5435,10 +5618,10 @@
         <v>119</v>
       </c>
       <c r="K56" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L56" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L56" s="54" t="s">
+        <v>260</v>
       </c>
       <c r="M56" s="38"/>
       <c r="N56" s="38"/>
@@ -5478,10 +5661,10 @@
         <v>119</v>
       </c>
       <c r="K57" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L57" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L57" s="54" t="s">
+        <v>261</v>
       </c>
       <c r="M57" s="38"/>
       <c r="N57" s="38"/>
@@ -5521,10 +5704,10 @@
         <v>119</v>
       </c>
       <c r="K58" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L58" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L58" s="54" t="s">
+        <v>262</v>
       </c>
       <c r="M58" s="38"/>
       <c r="N58" s="38"/>
@@ -5566,8 +5749,8 @@
       <c r="K59" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="L59" s="38" t="s">
-        <v>218</v>
+      <c r="L59" s="71" t="s">
+        <v>263</v>
       </c>
       <c r="M59" s="38"/>
       <c r="N59" s="38"/>
@@ -5609,8 +5792,8 @@
       <c r="K60" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="L60" s="38" t="s">
-        <v>218</v>
+      <c r="L60" s="71" t="s">
+        <v>263</v>
       </c>
       <c r="M60" s="38"/>
       <c r="N60" s="38"/>
@@ -5646,13 +5829,13 @@
         <v>45958</v>
       </c>
       <c r="G61" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="H61" s="48" t="s">
         <v>222</v>
       </c>
-      <c r="H61" s="48" t="s">
+      <c r="I61" s="49" t="s">
         <v>223</v>
-      </c>
-      <c r="I61" s="49" t="s">
-        <v>224</v>
       </c>
       <c r="J61" s="50" t="s">
         <v>54</v>
@@ -5697,10 +5880,10 @@
         <v>119</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L62" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L62" s="67" t="s">
+        <v>264</v>
       </c>
       <c r="M62" s="38"/>
       <c r="N62" s="38"/>
@@ -5730,19 +5913,19 @@
         <v>168</v>
       </c>
       <c r="E63" s="47" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F63" s="48">
         <v>45958</v>
       </c>
       <c r="G63" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="H63" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="H63" s="48" t="s">
+      <c r="I63" s="49" t="s">
         <v>226</v>
-      </c>
-      <c r="I63" s="49" t="s">
-        <v>227</v>
       </c>
       <c r="J63" s="50" t="s">
         <v>54</v>
@@ -5787,10 +5970,10 @@
         <v>119</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L64" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L64" s="67" t="s">
+        <v>265</v>
       </c>
       <c r="M64" s="38"/>
       <c r="N64" s="38"/>
@@ -5830,10 +6013,10 @@
         <v>119</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L65" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L65" s="67" t="s">
+        <v>266</v>
       </c>
       <c r="M65" s="38"/>
       <c r="N65" s="38"/>
@@ -5873,10 +6056,10 @@
         <v>119</v>
       </c>
       <c r="K66" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L66" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L66" s="70" t="s">
+        <v>267</v>
       </c>
       <c r="M66" s="38"/>
       <c r="N66" s="38"/>
@@ -5916,10 +6099,10 @@
         <v>119</v>
       </c>
       <c r="K67" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L67" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L67" s="67" t="s">
+        <v>268</v>
       </c>
       <c r="M67" s="38"/>
       <c r="N67" s="38"/>
@@ -5955,13 +6138,13 @@
         <v>45958</v>
       </c>
       <c r="G68" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="H68" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="H68" s="48" t="s">
+      <c r="I68" s="49" t="s">
         <v>229</v>
-      </c>
-      <c r="I68" s="49" t="s">
-        <v>230</v>
       </c>
       <c r="J68" s="50" t="s">
         <v>54</v>
@@ -6006,10 +6189,10 @@
         <v>119</v>
       </c>
       <c r="K69" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L69" s="38" t="s">
-        <v>218</v>
+        <v>122</v>
+      </c>
+      <c r="L69" s="72" t="s">
+        <v>269</v>
       </c>
       <c r="M69" s="38"/>
       <c r="N69" s="38"/>
@@ -6049,10 +6232,10 @@
         <v>119</v>
       </c>
       <c r="K70" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L70" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L70" s="70" t="s">
+        <v>270</v>
       </c>
       <c r="M70" s="38"/>
       <c r="N70" s="38"/>
@@ -6092,10 +6275,10 @@
         <v>119</v>
       </c>
       <c r="K71" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L71" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L71" s="67" t="s">
+        <v>271</v>
       </c>
       <c r="M71" s="38"/>
       <c r="N71" s="38"/>
@@ -6135,10 +6318,10 @@
         <v>119</v>
       </c>
       <c r="K72" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="L72" s="38" t="s">
-        <v>218</v>
+        <v>127</v>
+      </c>
+      <c r="L72" s="67" t="s">
+        <v>272</v>
       </c>
       <c r="M72" s="38"/>
       <c r="N72" s="38"/>
@@ -10192,13 +10375,13 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>L15 K14:L14 K17:L17 K66:L66 K70:L70 K10:L11 K20:L27 K59:L60 J10:J72 M10:N72 P10:R72</xm:sqref>
+          <xm:sqref>L10:L11 K17:L17 L20:L27 L66 P10:R72 L14:L16 K59:L60 J10:J72 M10:N72 L70</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3DE61C5E-9DA3-4CE3-A1FF-8FBE651EA6B5}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K71:K72 K67:K69 K61:K65 K28:K58 K18:K19 K15:K16 K12:K13</xm:sqref>
+          <xm:sqref>K61:K72 K10:K16 K18:K58</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
@@ -12441,12 +12624,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12708,21 +12894,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12747,18 +12939,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
